--- a/docs/table/报价测试数据/报价系统功能基础数据功能结构所需字段V2.xlsx
+++ b/docs/table/报价测试数据/报价系统功能基础数据功能结构所需字段V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\docs\table\报价测试数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F83B91E-E635-4F23-A490-82723D714C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F663E256-7DBA-4E69-83FA-DB085AE6F52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元素单价" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="150">
   <si>
     <t>客户名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -93,14 +93,6 @@
   </si>
   <si>
     <t>涨幅单位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -255,10 +247,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>投入料号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -267,10 +255,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2.非银点类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>客户编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -303,10 +287,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.银点类</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -413,14 +393,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>宏丰料号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -457,10 +429,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -493,22 +461,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回收费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财务管理费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财务管理费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回收费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>材料管理费</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -517,18 +469,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>包装费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>投入料号名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -565,10 +505,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>XXXXXXXX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>单价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -577,18 +513,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>运费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>货币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>货币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -609,14 +537,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>材料固定的涨幅值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -629,18 +549,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>包装费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>宏丰料号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -685,14 +593,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>XXXXXX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加工费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>项次</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -709,18 +609,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>冲压</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清洗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冷压焊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>投入料号名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -729,62 +617,58 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Z012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>基准值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CNY</t>
-  </si>
-  <si>
-    <t>CNY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NR2-25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H62接触板</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>支座</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AgNi10/Cu静触头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>热处理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material data tip</t>
+  </si>
+  <si>
+    <t>Material data tip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g/PCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RMB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外购件管理费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利润</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>税率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外购件1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外购件2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铆钉加工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外购件3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1253,7 +1137,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1274,13 +1158,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
@@ -1288,22 +1172,22 @@
         <v>8000137</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -1330,11 +1214,11 @@
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="4.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="3.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.375" customWidth="1"/>
+    <col min="8" max="8" width="14.25" customWidth="1"/>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
@@ -1342,286 +1226,158 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
+        <v>3120012530</v>
+      </c>
+      <c r="B2" s="4"/>
       <c r="C2" s="4">
-        <v>3111320634</v>
-      </c>
-      <c r="D2" s="4"/>
+        <v>10001</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>173</v>
-      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="H2" s="4">
-        <v>5</v>
+        <v>5.0990000000000002</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H3" s="4">
-        <v>2</v>
-      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4">
-        <v>3111320635</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4">
-        <v>3111320635</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="H5" s="4">
-        <v>5</v>
-      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B6" s="4">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3111320636</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="4">
-        <v>5</v>
-      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B7" s="4">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4">
-        <v>3111320636</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H7" s="4">
-        <v>2</v>
-      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B8" s="4">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4">
-        <v>3111320637</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B9" s="4">
-        <v>4</v>
-      </c>
-      <c r="C9" s="4">
-        <v>3111320637</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="4">
-        <v>2</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="H9" s="4">
-        <v>5</v>
-      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1649,95 +1405,91 @@
         <v>5</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B4" s="4">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B5" s="4">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>113</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1764,179 +1516,147 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E3" s="4">
         <v>2</v>
       </c>
       <c r="F3" s="4">
-        <v>3111320635</v>
+        <v>10003</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B4" s="4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E4" s="4">
         <v>3</v>
       </c>
       <c r="F4" s="4">
-        <v>3111320636</v>
+        <v>10001</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="H4" s="4">
         <v>1</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="4">
-        <v>4</v>
-      </c>
-      <c r="F5" s="4">
-        <v>3111320637</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4">
-        <v>3110520790</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="H6" s="4">
-        <v>2</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4">
-        <v>6</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1630010773</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
@@ -2348,40 +2068,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>8</v>
@@ -2389,179 +2109,123 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
       <c r="F2" s="4">
-        <v>1630010773</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
-        <v>123</v>
-      </c>
+        <v>10002</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>153</v>
-      </c>
+      <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M2" s="4">
-        <v>7.0000000000000001E-3</v>
+        <v>0.68920000000000003</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E3" s="4">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4">
+        <v>10003</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="4">
         <v>1</v>
       </c>
-      <c r="F3" s="4">
-        <v>1630010773</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="4">
-        <v>2</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>153</v>
-      </c>
+      <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="M3" s="4">
-        <v>2E-3</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1630010773</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="4">
-        <v>3</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1630010773</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="4">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2585,93 +2249,65 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="D2" s="4">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="4">
-        <v>3</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" s="4">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="4">
-        <v>12</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4">
-        <v>3</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2700,110 +2336,62 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1.4999999999999999E-2</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="4">
-        <v>1</v>
-      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2E-3</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="4">
-        <v>2</v>
-      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="4">
-        <v>3</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="4">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="4">
-        <v>2</v>
-      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2830,39 +2418,39 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4">
         <v>2000</v>
@@ -2871,16 +2459,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4">
         <v>3.1E-2</v>
@@ -2889,12 +2477,12 @@
         <v>0.4</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4">
         <v>2000</v>
@@ -2903,16 +2491,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="H3" s="4">
         <v>3.6999999999999998E-2</v>
@@ -2921,7 +2509,7 @@
         <v>0.1</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2950,55 +2538,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4">
         <v>2000</v>
       </c>
       <c r="D2" s="4">
-        <v>14</v>
-      </c>
-      <c r="E2" s="4">
-        <v>123</v>
-      </c>
+        <v>1.3959999999999999</v>
+      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0.5</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3020,64 +2604,40 @@
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B2" s="4">
-        <v>3</v>
+        <v>42.916699999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3111320634</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3111320635</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3111320636</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.8</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>3111320637</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.2</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>3110520790</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.6</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>1630010773</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.7</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
@@ -3189,43 +2749,35 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1.4999999999999999E-2</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="4">
-        <v>4</v>
-      </c>
+      <c r="G2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3248,51 +2800,49 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="7" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>10772736</v>
+      </c>
+      <c r="B2" s="4">
+        <v>10772736</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4">
+        <v>3120012530</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="4">
-        <v>102000966</v>
-      </c>
-      <c r="D2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="H2" s="4">
         <v>7.12</v>
@@ -3323,170 +2873,100 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>84</v>
-      </c>
       <c r="J1" s="9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="4">
-        <v>3111320634</v>
-      </c>
-      <c r="D2" s="4"/>
+        <v>10001</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="E2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="4">
-        <v>5</v>
-      </c>
-      <c r="J2" s="4">
-        <v>2</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4">
-        <v>3111320635</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="4">
-        <v>50</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" s="4">
-        <v>5</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1</v>
-      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4">
-        <v>3111320636</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="4">
-        <v>5</v>
-      </c>
-      <c r="J4" s="4">
-        <v>2</v>
-      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B5" s="4">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4">
-        <v>3111320637</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="4">
-        <v>50</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="4">
-        <v>5</v>
-      </c>
-      <c r="J5" s="4">
-        <v>1</v>
-      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B6" s="4">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3110520790</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -3834,7 +3314,7 @@
   <cols>
     <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.25" customWidth="1"/>
     <col min="4" max="4" width="5.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
@@ -3847,184 +3327,142 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="G1" s="9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B2" s="4">
-        <v>3111320634</v>
-      </c>
-      <c r="C2" s="4"/>
+        <v>10001</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="4">
-        <v>100</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
+      <c r="J2" s="4">
+        <v>5.97</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3120018220</v>
+        <v>3120012530</v>
       </c>
       <c r="B3" s="4">
-        <v>3111320635</v>
-      </c>
-      <c r="C3" s="4"/>
+        <v>10001</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="D3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="4">
-        <v>100</v>
-      </c>
-      <c r="G3" s="4">
-        <v>6</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
+      <c r="J3" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3111320636</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4" s="4">
-        <v>100</v>
-      </c>
-      <c r="G4" s="4">
-        <v>7</v>
-      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3111320637</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F5" s="4">
-        <v>100</v>
-      </c>
-      <c r="G5" s="4">
-        <v>8</v>
-      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B6" s="4">
-        <v>3110520790</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="4">
-        <v>73</v>
-      </c>
-      <c r="G6" s="4">
-        <v>4</v>
-      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B7" s="4">
-        <v>3110520790</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="4">
-        <v>27</v>
-      </c>
-      <c r="G7" s="4">
-        <v>5</v>
-      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -4392,128 +3830,68 @@
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
       <c r="C2" s="4"/>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="4">
-        <v>5</v>
-      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B3" s="4">
-        <v>3111320635</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="4">
-        <v>10</v>
-      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3111320636</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4" s="4">
-        <v>8</v>
-      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3111320637</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F5" s="4">
-        <v>10</v>
-      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B6" s="4">
-        <v>3110520790</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="4">
-        <v>4</v>
-      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B7" s="4">
-        <v>3110520790</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="4">
-        <v>5</v>
-      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4546,208 +3924,116 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4">
-        <v>2</v>
-      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="J2" s="4">
-        <v>5</v>
-      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4">
-        <v>3111320635</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4">
-        <v>3</v>
-      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="4">
-        <v>10</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>134</v>
-      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
     <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4">
-        <v>3111320636</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4">
-        <v>4</v>
-      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="J4" s="4">
-        <v>5</v>
-      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4">
-        <v>3111320637</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="4">
-        <v>5</v>
-      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="4">
-        <v>10</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3110520790</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4">
-        <v>8</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="4">
-        <v>10</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="C7" s="4"/>
@@ -4770,7 +4056,7 @@
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.875" customWidth="1"/>
     <col min="8" max="8" width="10.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.125" bestFit="1" customWidth="1"/>
@@ -4781,232 +4067,128 @@
         <v>5</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>106</v>
-      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="4">
-        <v>3</v>
-      </c>
+      <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>105</v>
-      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="4">
-        <v>5</v>
-      </c>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>109</v>
-      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="4">
-        <v>2</v>
-      </c>
+      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="4">
-        <v>3</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.4</v>
-      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>141</v>
-      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3111320635</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>106</v>
-      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="4">
-        <v>3</v>
-      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4">
-        <v>3111320635</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>105</v>
-      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4">
-        <v>5</v>
-      </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B8" s="4">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4">
-        <v>3111320635</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="4">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>109</v>
-      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="4">
-        <v>23</v>
-      </c>
+      <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4">
-        <v>3110520790</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="4">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.4</v>
-      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
@@ -5359,88 +4541,56 @@
         <v>5</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4">
-        <v>1.4999999999999999E-2</v>
-      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="4">
-        <v>1</v>
-      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4">
-        <v>3</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="4">
-        <v>2</v>
-      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5465,32 +4615,24 @@
         <v>5</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>3120018220</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>3111320634</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4">
-        <v>10</v>
-      </c>
+      <c r="E2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
